--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1948,6 +1948,594 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122514396</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Johannelund, Johannelund, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>713375</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6635143</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122514502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Johannelund, Johannelund, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>713376</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6635122</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122514479</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Johannelund, Johannelund, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>713370</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6635115</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122514469</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>713375</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6635125</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122514487</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>713377</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6635112</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514396</v>
+        <v>122514502</v>
       </c>
       <c r="B13" t="n">
         <v>98211</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1993,18 +1993,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R13" t="n">
-        <v>6635143</v>
+        <v>6635122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,40 +2032,49 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,11 +2089,6 @@
       <c r="E14" t="n">
         <v>220787</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2099,7 +2101,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2114,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,19 +2153,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514479</v>
+        <v>122514487</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,11 +2200,6 @@
       <c r="E15" t="n">
         <v>220787</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2225,7 +2212,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2240,14 +2227,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713370</v>
+        <v>713377</v>
       </c>
       <c r="R15" t="n">
-        <v>6635115</v>
+        <v>6635112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,19 +2264,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,19 +2281,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514469</v>
+        <v>122514479</v>
       </c>
       <c r="B16" t="n">
         <v>98211</v>
@@ -2346,7 +2323,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,14 +2338,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R16" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,9 +2375,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,19 +2402,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514487</v>
+        <v>122514396</v>
       </c>
       <c r="B17" t="n">
         <v>98211</v>
@@ -2457,7 +2444,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2470,16 +2457,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635112</v>
+        <v>6635143</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,6 +2509,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -2293,7 +2293,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514479</v>
+        <v>122514396</v>
       </c>
       <c r="B16" t="n">
         <v>98211</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2336,16 +2336,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635115</v>
+        <v>6635143</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,46 +2377,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514396</v>
+        <v>122514479</v>
       </c>
       <c r="B17" t="n">
         <v>98211</v>
@@ -2444,7 +2437,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2457,18 +2450,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R17" t="n">
-        <v>6635143</v>
+        <v>6635115</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,30 +2489,39 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,6 +1968,11 @@
       <c r="E13" t="n">
         <v>220787</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1980,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,14 +2000,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R13" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,19 +2037,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,22 +2054,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514469</v>
+        <v>122514479</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,6 +2084,11 @@
       <c r="E14" t="n">
         <v>220787</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2116,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R14" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,9 +2153,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,12 +2180,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2185,7 +2195,7 @@
         <v>122514487</v>
       </c>
       <c r="B15" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,6 +2209,11 @@
       </c>
       <c r="E15" t="n">
         <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2293,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514396</v>
+        <v>122514502</v>
       </c>
       <c r="B16" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,6 +2326,11 @@
       <c r="E16" t="n">
         <v>220787</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2323,7 +2343,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2336,18 +2356,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R16" t="n">
-        <v>6635143</v>
+        <v>6635122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,40 +2395,49 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514479</v>
+        <v>122514396</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,6 +2452,11 @@
       <c r="E17" t="n">
         <v>220787</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2437,7 +2469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2450,16 +2482,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635115</v>
+        <v>6635143</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,39 +2523,30 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R13" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,7 +2069,7 @@
         <v>122514479</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514487</v>
+        <v>122514502</v>
       </c>
       <c r="B15" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2242,14 +2242,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713377</v>
+        <v>713376</v>
       </c>
       <c r="R15" t="n">
-        <v>6635112</v>
+        <v>6635122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,9 +2279,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,22 +2306,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2358,14 +2368,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,19 +2405,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,12 +2422,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
         <v>122514396</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514487</v>
+        <v>122514502</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713377</v>
+        <v>713376</v>
       </c>
       <c r="R13" t="n">
-        <v>6635112</v>
+        <v>6635122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,9 +2037,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,19 +2064,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514479</v>
+        <v>122514396</v>
       </c>
       <c r="B14" t="n">
         <v>98237</v>
@@ -2101,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2114,16 +2124,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635115</v>
+        <v>6635143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,46 +2165,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2227,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2242,14 +2245,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R15" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,19 +2282,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,19 +2299,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514469</v>
+        <v>122514479</v>
       </c>
       <c r="B16" t="n">
         <v>98237</v>
@@ -2353,7 +2346,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2368,14 +2361,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R16" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,9 +2398,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,19 +2425,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514396</v>
+        <v>122514487</v>
       </c>
       <c r="B17" t="n">
         <v>98237</v>
@@ -2469,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,18 +2485,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R17" t="n">
-        <v>6635143</v>
+        <v>6635112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2535,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514502</v>
+        <v>122514479</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713376</v>
+        <v>713370</v>
       </c>
       <c r="R13" t="n">
-        <v>6635122</v>
+        <v>6635115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514396</v>
+        <v>122514502</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,18 +2124,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R14" t="n">
-        <v>6635143</v>
+        <v>6635122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,40 +2163,49 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,7 +2237,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2249,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R15" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514479</v>
+        <v>122514469</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,14 +2368,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635115</v>
+        <v>6635125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,19 +2405,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,22 +2422,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514487</v>
+        <v>122514396</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,7 +2469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2485,16 +2482,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635112</v>
+        <v>6635143</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,6 +2534,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514502</v>
+        <v>122514396</v>
       </c>
       <c r="B14" t="n">
         <v>98240</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,16 +2124,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635122</v>
+        <v>6635143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,46 +2165,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514487</v>
+        <v>122514469</v>
       </c>
       <c r="B15" t="n">
         <v>98240</v>
@@ -2237,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2256,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R15" t="n">
-        <v>6635112</v>
+        <v>6635125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,7 +2311,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B16" t="n">
         <v>98240</v>
@@ -2353,7 +2346,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2372,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R16" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2434,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514396</v>
+        <v>122514502</v>
       </c>
       <c r="B17" t="n">
         <v>98240</v>
@@ -2469,7 +2462,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,18 +2475,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R17" t="n">
-        <v>6635143</v>
+        <v>6635122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,30 +2514,39 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>122514479</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514396</v>
+        <v>122514469</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,18 +2124,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635143</v>
+        <v>6635125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2174,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2195,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514469</v>
+        <v>122514502</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2245,14 +2242,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R15" t="n">
-        <v>6635125</v>
+        <v>6635122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,9 +2279,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,22 +2306,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514487</v>
+        <v>122514396</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2359,16 +2366,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635112</v>
+        <v>6635143</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,6 +2418,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514502</v>
+        <v>122514487</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2477,14 +2487,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713376</v>
+        <v>713377</v>
       </c>
       <c r="R17" t="n">
-        <v>6635122</v>
+        <v>6635112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2514,19 +2524,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,12 +2541,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514479</v>
+        <v>122514469</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R13" t="n">
-        <v>6635115</v>
+        <v>6635125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,19 +2037,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,22 +2054,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514469</v>
+        <v>122514502</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,7 +2101,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2126,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R14" t="n">
-        <v>6635125</v>
+        <v>6635122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,9 +2153,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,22 +2180,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514502</v>
+        <v>122514487</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2242,14 +2242,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713376</v>
+        <v>713377</v>
       </c>
       <c r="R15" t="n">
-        <v>6635122</v>
+        <v>6635112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,19 +2279,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,12 +2296,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2321,7 +2311,7 @@
         <v>122514396</v>
       </c>
       <c r="B16" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2437,10 +2427,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514487</v>
+        <v>122514479</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,7 +2462,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2487,14 +2477,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713377</v>
+        <v>713370</v>
       </c>
       <c r="R17" t="n">
-        <v>6635112</v>
+        <v>6635115</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,9 +2514,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,12 +2541,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514469</v>
+        <v>122514502</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R13" t="n">
-        <v>6635125</v>
+        <v>6635122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,9 +2037,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,19 +2064,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514502</v>
+        <v>122514396</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2101,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2114,16 +2124,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635122</v>
+        <v>6635143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,46 +2165,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514487</v>
+        <v>122514479</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2227,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2242,14 +2245,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713377</v>
+        <v>713370</v>
       </c>
       <c r="R15" t="n">
-        <v>6635112</v>
+        <v>6635115</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,9 +2282,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,19 +2309,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514396</v>
+        <v>122514487</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2343,7 +2356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2356,18 +2369,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R16" t="n">
-        <v>6635143</v>
+        <v>6635112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2419,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,7 +2437,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514479</v>
+        <v>122514469</v>
       </c>
       <c r="B17" t="n">
         <v>98244</v>
@@ -2462,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2477,14 +2487,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635115</v>
+        <v>6635125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2514,19 +2524,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,12 +2541,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -2321,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514487</v>
+        <v>122514469</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635112</v>
+        <v>6635125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B17" t="n">
         <v>98244</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R17" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -2321,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R16" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514487</v>
+        <v>122514469</v>
       </c>
       <c r="B17" t="n">
         <v>98244</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635112</v>
+        <v>6635125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514479</v>
+        <v>122514502</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713370</v>
+        <v>713376</v>
       </c>
       <c r="R13" t="n">
-        <v>6635115</v>
+        <v>6635122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514469</v>
+        <v>122514479</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2126,14 +2126,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R14" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,9 +2163,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,22 +2190,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,7 +2237,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2242,14 +2252,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R15" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,19 +2289,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,22 +2306,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514396</v>
+        <v>122514487</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2366,18 +2366,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R16" t="n">
-        <v>6635143</v>
+        <v>6635112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2418,7 +2416,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2437,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514487</v>
+        <v>122514396</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,7 +2469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2485,16 +2482,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R17" t="n">
-        <v>6635112</v>
+        <v>6635143</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,6 +2534,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514502</v>
+        <v>122514396</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1998,16 +1998,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R13" t="n">
-        <v>6635122</v>
+        <v>6635143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,46 +2039,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514479</v>
+        <v>122514502</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2111,7 +2104,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2130,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713370</v>
+        <v>713376</v>
       </c>
       <c r="R14" t="n">
-        <v>6635115</v>
+        <v>6635122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,7 +2195,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514469</v>
+        <v>122514479</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2237,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2252,14 +2245,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R15" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,9 +2282,19 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,19 +2309,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514487</v>
+        <v>122514469</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2353,7 +2356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2372,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713377</v>
+        <v>713375</v>
       </c>
       <c r="R16" t="n">
-        <v>6635112</v>
+        <v>6635125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2434,7 +2437,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514396</v>
+        <v>122514487</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2469,7 +2472,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2482,18 +2485,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R17" t="n">
-        <v>6635143</v>
+        <v>6635112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2535,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514396</v>
+        <v>122514479</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1998,18 +1998,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713375</v>
+        <v>713370</v>
       </c>
       <c r="R13" t="n">
-        <v>6635143</v>
+        <v>6635115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,40 +2037,49 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514502</v>
+        <v>122514396</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,7 +2111,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2117,16 +2124,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R14" t="n">
-        <v>6635122</v>
+        <v>6635143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,49 +2165,40 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514479</v>
+        <v>122514502</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713370</v>
+        <v>713376</v>
       </c>
       <c r="R15" t="n">
-        <v>6635115</v>
+        <v>6635122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,7 +2324,7 @@
         <v>122514469</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>122514487</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 51476-2023 artfynd.xlsx
+++ b/artfynd/A 51476-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113397625</v>
+        <v>122514479</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1870,14 +1870,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Johannelund, 100m NV om (*knärot* /stjälk/), Upl</t>
+          <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713373</v>
+        <v>713370</v>
       </c>
       <c r="R12" t="n">
-        <v>6635125</v>
+        <v>6635115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,24 +1902,24 @@
           <t>Roslags-Bro</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>AB-Nor-1806</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Johanneslund, Obskoord: 6634820/1668289/15 m (Avst fr FV-lokal: 12 m).</t>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,23 +1934,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514479</v>
+        <v>122514396</v>
       </c>
       <c r="B13" t="n">
         <v>98357</v>
@@ -1985,7 +1981,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1998,16 +1994,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713370</v>
+        <v>713375</v>
       </c>
       <c r="R13" t="n">
-        <v>6635115</v>
+        <v>6635143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,46 +2035,37 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514396</v>
+        <v>122514502</v>
       </c>
       <c r="B14" t="n">
         <v>98357</v>
@@ -2111,7 +2100,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2124,18 +2113,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Johannelund, Johannelund, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713375</v>
+        <v>713376</v>
       </c>
       <c r="R14" t="n">
-        <v>6635143</v>
+        <v>6635122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,37 +2152,46 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122514502</v>
+        <v>122514469</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2230,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2245,14 +2241,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Johannelund, Johannelund, Upl</t>
+          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713376</v>
+        <v>713375</v>
       </c>
       <c r="R15" t="n">
-        <v>6635122</v>
+        <v>6635125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,19 +2278,9 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,19 +2295,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514469</v>
+        <v>122514487</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2356,7 +2342,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713375</v>
+        <v>713377</v>
       </c>
       <c r="R16" t="n">
-        <v>6635125</v>
+        <v>6635112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2434,122 +2420,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>122514487</v>
-      </c>
-      <c r="B17" t="n">
-        <v>98357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Johannelund, 100m NV om, Johannelund, 100m NV om, Upl</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>713377</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6635112</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Roslags-Bro</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
